--- a/1111_lite.xlsx
+++ b/1111_lite.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMINN\Documents\auroradist\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7274FB35-1766-44EA-B626-C35F46102BDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4A079BD-2688-4FAB-9078-6286FB72D76B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17790" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2883" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2883" uniqueCount="203">
   <si>
     <t>Licensor</t>
   </si>
@@ -581,9 +581,6 @@
     <t>KPS010</t>
   </si>
   <si>
-    <t>UK6822111310</t>
-  </si>
-  <si>
     <t>A549606399629689</t>
   </si>
   <si>
@@ -602,9 +599,6 @@
     <t>KPS011</t>
   </si>
   <si>
-    <t>UK6822111311</t>
-  </si>
-  <si>
     <t>A744352074198212</t>
   </si>
   <si>
@@ -633,6 +627,9 @@
   </si>
   <si>
     <t>Mon Oct 17 22:05:07 2022</t>
+  </si>
+  <si>
+    <t>GXBDT2502458</t>
   </si>
 </sst>
 </file>
@@ -643,7 +640,7 @@
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -655,6 +652,18 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF6B7280"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -680,12 +689,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -997,6 +1007,7 @@
     <col min="2" max="2" width="30.7109375" customWidth="1"/>
     <col min="3" max="4" width="10.7109375" style="2" customWidth="1"/>
     <col min="6" max="6" width="20.7109375" style="3" customWidth="1"/>
+    <col min="16" max="16" width="12.28515625" bestFit="1" customWidth="1"/>
     <col min="71" max="71" width="12.7109375" style="3" customWidth="1"/>
     <col min="72" max="74" width="12.7109375" style="4" customWidth="1"/>
     <col min="75" max="75" width="15.7109375" customWidth="1"/>
@@ -1266,7 +1277,7 @@
       <c r="O2" t="s">
         <v>66</v>
       </c>
-      <c r="P2">
+      <c r="P2" s="5">
         <v>5057805794592</v>
       </c>
       <c r="Q2" t="s">
@@ -1423,7 +1434,7 @@
       <c r="N4" t="s">
         <v>65</v>
       </c>
-      <c r="P4">
+      <c r="P4" s="5">
         <v>5057805794592</v>
       </c>
       <c r="Q4" t="s">
@@ -1589,7 +1600,7 @@
       <c r="N6" t="s">
         <v>65</v>
       </c>
-      <c r="P6">
+      <c r="P6" s="5">
         <v>5057805794592</v>
       </c>
       <c r="Q6" t="s">
@@ -1755,7 +1766,7 @@
       <c r="N8" t="s">
         <v>65</v>
       </c>
-      <c r="P8">
+      <c r="P8" s="5">
         <v>5057805794592</v>
       </c>
       <c r="Q8" t="s">
@@ -1833,7 +1844,7 @@
         <v>65</v>
       </c>
       <c r="P9">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q9" t="s">
         <v>83</v>
@@ -1909,8 +1920,8 @@
       <c r="N10" t="s">
         <v>65</v>
       </c>
-      <c r="P10">
-        <v>5057805794608</v>
+      <c r="P10" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q10" t="s">
         <v>83</v>
@@ -1987,7 +1998,7 @@
         <v>65</v>
       </c>
       <c r="P11">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q11" t="s">
         <v>83</v>
@@ -2063,8 +2074,8 @@
       <c r="N12" t="s">
         <v>65</v>
       </c>
-      <c r="P12">
-        <v>5057805794608</v>
+      <c r="P12" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q12" t="s">
         <v>83</v>
@@ -2141,7 +2152,7 @@
         <v>65</v>
       </c>
       <c r="P13">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q13" t="s">
         <v>83</v>
@@ -2217,8 +2228,8 @@
       <c r="N14" t="s">
         <v>65</v>
       </c>
-      <c r="P14">
-        <v>5057805794608</v>
+      <c r="P14" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q14" t="s">
         <v>83</v>
@@ -2295,7 +2306,7 @@
         <v>65</v>
       </c>
       <c r="P15">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q15" t="s">
         <v>83</v>
@@ -2371,8 +2382,8 @@
       <c r="N16" t="s">
         <v>65</v>
       </c>
-      <c r="P16">
-        <v>5057805794608</v>
+      <c r="P16" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q16" t="s">
         <v>83</v>
@@ -2449,7 +2460,7 @@
         <v>65</v>
       </c>
       <c r="P17">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q17" t="s">
         <v>83</v>
@@ -2525,8 +2536,8 @@
       <c r="N18" t="s">
         <v>65</v>
       </c>
-      <c r="P18">
-        <v>5057805794608</v>
+      <c r="P18" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q18" t="s">
         <v>83</v>
@@ -2603,7 +2614,7 @@
         <v>65</v>
       </c>
       <c r="P19">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q19" t="s">
         <v>83</v>
@@ -2679,8 +2690,8 @@
       <c r="N20" t="s">
         <v>65</v>
       </c>
-      <c r="P20">
-        <v>5057805794608</v>
+      <c r="P20" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q20" t="s">
         <v>83</v>
@@ -2757,7 +2768,7 @@
         <v>65</v>
       </c>
       <c r="P21">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q21" t="s">
         <v>83</v>
@@ -2833,8 +2844,8 @@
       <c r="N22" t="s">
         <v>65</v>
       </c>
-      <c r="P22">
-        <v>5057805794608</v>
+      <c r="P22" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q22" t="s">
         <v>83</v>
@@ -2911,7 +2922,7 @@
         <v>65</v>
       </c>
       <c r="P23">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q23" t="s">
         <v>83</v>
@@ -2987,8 +2998,8 @@
       <c r="N24" t="s">
         <v>65</v>
       </c>
-      <c r="P24">
-        <v>5057805794608</v>
+      <c r="P24" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q24" t="s">
         <v>83</v>
@@ -3065,7 +3076,7 @@
         <v>65</v>
       </c>
       <c r="P25">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q25" t="s">
         <v>83</v>
@@ -3141,8 +3152,8 @@
       <c r="N26" t="s">
         <v>65</v>
       </c>
-      <c r="P26">
-        <v>5057805794608</v>
+      <c r="P26" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q26" t="s">
         <v>83</v>
@@ -3219,7 +3230,7 @@
         <v>65</v>
       </c>
       <c r="P27">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q27" t="s">
         <v>83</v>
@@ -3295,8 +3306,8 @@
       <c r="N28" t="s">
         <v>65</v>
       </c>
-      <c r="P28">
-        <v>5057805794608</v>
+      <c r="P28" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q28" t="s">
         <v>83</v>
@@ -3373,7 +3384,7 @@
         <v>65</v>
       </c>
       <c r="P29">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q29" t="s">
         <v>83</v>
@@ -3449,8 +3460,8 @@
       <c r="N30" t="s">
         <v>65</v>
       </c>
-      <c r="P30">
-        <v>5057805794608</v>
+      <c r="P30" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q30" t="s">
         <v>83</v>
@@ -3527,7 +3538,7 @@
         <v>65</v>
       </c>
       <c r="P31">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q31" t="s">
         <v>83</v>
@@ -3603,8 +3614,8 @@
       <c r="N32" t="s">
         <v>65</v>
       </c>
-      <c r="P32">
-        <v>5057805794608</v>
+      <c r="P32" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q32" t="s">
         <v>83</v>
@@ -3681,7 +3692,7 @@
         <v>65</v>
       </c>
       <c r="P33">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q33" t="s">
         <v>83</v>
@@ -3757,8 +3768,8 @@
       <c r="N34" t="s">
         <v>65</v>
       </c>
-      <c r="P34">
-        <v>5057805794608</v>
+      <c r="P34" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q34" t="s">
         <v>83</v>
@@ -3835,7 +3846,7 @@
         <v>65</v>
       </c>
       <c r="P35">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q35" t="s">
         <v>83</v>
@@ -3911,8 +3922,8 @@
       <c r="N36" t="s">
         <v>65</v>
       </c>
-      <c r="P36">
-        <v>5057805794608</v>
+      <c r="P36" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q36" t="s">
         <v>83</v>
@@ -3989,7 +4000,7 @@
         <v>65</v>
       </c>
       <c r="P37">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q37" t="s">
         <v>83</v>
@@ -4065,8 +4076,8 @@
       <c r="N38" t="s">
         <v>65</v>
       </c>
-      <c r="P38">
-        <v>5057805794608</v>
+      <c r="P38" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q38" t="s">
         <v>83</v>
@@ -4143,7 +4154,7 @@
         <v>65</v>
       </c>
       <c r="P39">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q39" t="s">
         <v>83</v>
@@ -4219,8 +4230,8 @@
       <c r="N40" t="s">
         <v>65</v>
       </c>
-      <c r="P40">
-        <v>5057805794608</v>
+      <c r="P40" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q40" t="s">
         <v>83</v>
@@ -4297,7 +4308,7 @@
         <v>65</v>
       </c>
       <c r="P41">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q41" t="s">
         <v>83</v>
@@ -4373,8 +4384,8 @@
       <c r="N42" t="s">
         <v>65</v>
       </c>
-      <c r="P42">
-        <v>5057805794608</v>
+      <c r="P42" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q42" t="s">
         <v>83</v>
@@ -4451,7 +4462,7 @@
         <v>65</v>
       </c>
       <c r="P43">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q43" t="s">
         <v>83</v>
@@ -4527,8 +4538,8 @@
       <c r="N44" t="s">
         <v>65</v>
       </c>
-      <c r="P44">
-        <v>5057805794608</v>
+      <c r="P44" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q44" t="s">
         <v>83</v>
@@ -4605,7 +4616,7 @@
         <v>65</v>
       </c>
       <c r="P45">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q45" t="s">
         <v>83</v>
@@ -4681,8 +4692,8 @@
       <c r="N46" t="s">
         <v>65</v>
       </c>
-      <c r="P46">
-        <v>5057805794608</v>
+      <c r="P46" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q46" t="s">
         <v>83</v>
@@ -4759,7 +4770,7 @@
         <v>65</v>
       </c>
       <c r="P47">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q47" t="s">
         <v>83</v>
@@ -4835,8 +4846,8 @@
       <c r="N48" t="s">
         <v>65</v>
       </c>
-      <c r="P48">
-        <v>5057805794608</v>
+      <c r="P48" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q48" t="s">
         <v>83</v>
@@ -4913,7 +4924,7 @@
         <v>65</v>
       </c>
       <c r="P49">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q49" t="s">
         <v>83</v>
@@ -4989,8 +5000,8 @@
       <c r="N50" t="s">
         <v>65</v>
       </c>
-      <c r="P50">
-        <v>5057805794608</v>
+      <c r="P50" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q50" t="s">
         <v>83</v>
@@ -5067,7 +5078,7 @@
         <v>65</v>
       </c>
       <c r="P51">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q51" t="s">
         <v>83</v>
@@ -5143,8 +5154,8 @@
       <c r="N52" t="s">
         <v>65</v>
       </c>
-      <c r="P52">
-        <v>5057805794608</v>
+      <c r="P52" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q52" t="s">
         <v>83</v>
@@ -5221,7 +5232,7 @@
         <v>65</v>
       </c>
       <c r="P53">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q53" t="s">
         <v>83</v>
@@ -5297,8 +5308,8 @@
       <c r="N54" t="s">
         <v>65</v>
       </c>
-      <c r="P54">
-        <v>5057805794608</v>
+      <c r="P54" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q54" t="s">
         <v>83</v>
@@ -5375,7 +5386,7 @@
         <v>65</v>
       </c>
       <c r="P55">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q55" t="s">
         <v>83</v>
@@ -5451,8 +5462,8 @@
       <c r="N56" t="s">
         <v>65</v>
       </c>
-      <c r="P56">
-        <v>5057805794608</v>
+      <c r="P56" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q56" t="s">
         <v>83</v>
@@ -5529,7 +5540,7 @@
         <v>65</v>
       </c>
       <c r="P57">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q57" t="s">
         <v>83</v>
@@ -5605,8 +5616,8 @@
       <c r="N58" t="s">
         <v>65</v>
       </c>
-      <c r="P58">
-        <v>5057805794608</v>
+      <c r="P58" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q58" t="s">
         <v>83</v>
@@ -5683,7 +5694,7 @@
         <v>65</v>
       </c>
       <c r="P59">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q59" t="s">
         <v>83</v>
@@ -5759,8 +5770,8 @@
       <c r="N60" t="s">
         <v>65</v>
       </c>
-      <c r="P60">
-        <v>5057805794608</v>
+      <c r="P60" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q60" t="s">
         <v>83</v>
@@ -5837,7 +5848,7 @@
         <v>65</v>
       </c>
       <c r="P61">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q61" t="s">
         <v>83</v>
@@ -5913,8 +5924,8 @@
       <c r="N62" t="s">
         <v>65</v>
       </c>
-      <c r="P62">
-        <v>5057805794608</v>
+      <c r="P62" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q62" t="s">
         <v>83</v>
@@ -5991,7 +6002,7 @@
         <v>65</v>
       </c>
       <c r="P63">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q63" t="s">
         <v>83</v>
@@ -6067,8 +6078,8 @@
       <c r="N64" t="s">
         <v>65</v>
       </c>
-      <c r="P64">
-        <v>5057805794608</v>
+      <c r="P64" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q64" t="s">
         <v>83</v>
@@ -6145,7 +6156,7 @@
         <v>65</v>
       </c>
       <c r="P65">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q65" t="s">
         <v>83</v>
@@ -6221,8 +6232,8 @@
       <c r="N66" t="s">
         <v>65</v>
       </c>
-      <c r="P66">
-        <v>5057805794608</v>
+      <c r="P66" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q66" t="s">
         <v>83</v>
@@ -6299,7 +6310,7 @@
         <v>65</v>
       </c>
       <c r="P67">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q67" t="s">
         <v>83</v>
@@ -6375,8 +6386,8 @@
       <c r="N68" t="s">
         <v>65</v>
       </c>
-      <c r="P68">
-        <v>5057805794608</v>
+      <c r="P68" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q68" t="s">
         <v>83</v>
@@ -6453,7 +6464,7 @@
         <v>65</v>
       </c>
       <c r="P69">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q69" t="s">
         <v>83</v>
@@ -6529,8 +6540,8 @@
       <c r="N70" t="s">
         <v>65</v>
       </c>
-      <c r="P70">
-        <v>5057805794608</v>
+      <c r="P70" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q70" t="s">
         <v>83</v>
@@ -6607,7 +6618,7 @@
         <v>65</v>
       </c>
       <c r="P71">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q71" t="s">
         <v>83</v>
@@ -6683,8 +6694,8 @@
       <c r="N72" t="s">
         <v>65</v>
       </c>
-      <c r="P72">
-        <v>5057805794608</v>
+      <c r="P72" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q72" t="s">
         <v>83</v>
@@ -6761,7 +6772,7 @@
         <v>65</v>
       </c>
       <c r="P73">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q73" t="s">
         <v>83</v>
@@ -6837,8 +6848,8 @@
       <c r="N74" t="s">
         <v>65</v>
       </c>
-      <c r="P74">
-        <v>5057805794608</v>
+      <c r="P74" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q74" t="s">
         <v>83</v>
@@ -6915,7 +6926,7 @@
         <v>65</v>
       </c>
       <c r="P75">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q75" t="s">
         <v>83</v>
@@ -6991,8 +7002,8 @@
       <c r="N76" t="s">
         <v>65</v>
       </c>
-      <c r="P76">
-        <v>5057805794608</v>
+      <c r="P76" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q76" t="s">
         <v>83</v>
@@ -7069,7 +7080,7 @@
         <v>65</v>
       </c>
       <c r="P77">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q77" t="s">
         <v>83</v>
@@ -7145,8 +7156,8 @@
       <c r="N78" t="s">
         <v>65</v>
       </c>
-      <c r="P78">
-        <v>5057805794608</v>
+      <c r="P78" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q78" t="s">
         <v>83</v>
@@ -7223,7 +7234,7 @@
         <v>65</v>
       </c>
       <c r="P79">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q79" t="s">
         <v>83</v>
@@ -7299,8 +7310,8 @@
       <c r="N80" t="s">
         <v>65</v>
       </c>
-      <c r="P80">
-        <v>5057805794608</v>
+      <c r="P80" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q80" t="s">
         <v>83</v>
@@ -7377,7 +7388,7 @@
         <v>65</v>
       </c>
       <c r="P81">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q81" t="s">
         <v>83</v>
@@ -7453,8 +7464,8 @@
       <c r="N82" t="s">
         <v>65</v>
       </c>
-      <c r="P82">
-        <v>5057805794608</v>
+      <c r="P82" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q82" t="s">
         <v>83</v>
@@ -7531,7 +7542,7 @@
         <v>65</v>
       </c>
       <c r="P83">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q83" t="s">
         <v>83</v>
@@ -7607,8 +7618,8 @@
       <c r="N84" t="s">
         <v>65</v>
       </c>
-      <c r="P84">
-        <v>5057805794608</v>
+      <c r="P84" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q84" t="s">
         <v>83</v>
@@ -7685,7 +7696,7 @@
         <v>65</v>
       </c>
       <c r="P85">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q85" t="s">
         <v>83</v>
@@ -7761,8 +7772,8 @@
       <c r="N86" t="s">
         <v>65</v>
       </c>
-      <c r="P86">
-        <v>5057805794608</v>
+      <c r="P86" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q86" t="s">
         <v>83</v>
@@ -7839,7 +7850,7 @@
         <v>65</v>
       </c>
       <c r="P87">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q87" t="s">
         <v>83</v>
@@ -7915,8 +7926,8 @@
       <c r="N88" t="s">
         <v>65</v>
       </c>
-      <c r="P88">
-        <v>5057805794608</v>
+      <c r="P88" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q88" t="s">
         <v>83</v>
@@ -7993,7 +8004,7 @@
         <v>65</v>
       </c>
       <c r="P89">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q89" t="s">
         <v>83</v>
@@ -8069,8 +8080,8 @@
       <c r="N90" t="s">
         <v>65</v>
       </c>
-      <c r="P90">
-        <v>5057805794608</v>
+      <c r="P90" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q90" t="s">
         <v>83</v>
@@ -8147,7 +8158,7 @@
         <v>65</v>
       </c>
       <c r="P91">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q91" t="s">
         <v>83</v>
@@ -8223,8 +8234,8 @@
       <c r="N92" t="s">
         <v>65</v>
       </c>
-      <c r="P92">
-        <v>5057805794608</v>
+      <c r="P92" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q92" t="s">
         <v>83</v>
@@ -8301,13 +8312,13 @@
         <v>65</v>
       </c>
       <c r="P93">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q93" t="s">
         <v>83</v>
       </c>
       <c r="R93" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="V93">
         <v>124</v>
@@ -8377,14 +8388,14 @@
       <c r="N94" t="s">
         <v>65</v>
       </c>
-      <c r="P94">
-        <v>5057805794608</v>
+      <c r="P94" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q94" t="s">
         <v>83</v>
       </c>
       <c r="R94" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="V94">
         <v>0</v>
@@ -8455,13 +8466,13 @@
         <v>65</v>
       </c>
       <c r="P95">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q95" t="s">
         <v>83</v>
       </c>
       <c r="R95" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="V95">
         <v>14</v>
@@ -8531,14 +8542,14 @@
       <c r="N96" t="s">
         <v>65</v>
       </c>
-      <c r="P96">
-        <v>5057805794608</v>
+      <c r="P96" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q96" t="s">
         <v>83</v>
       </c>
       <c r="R96" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="V96">
         <v>0</v>
@@ -8609,13 +8620,13 @@
         <v>65</v>
       </c>
       <c r="P97">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q97" t="s">
         <v>83</v>
       </c>
       <c r="R97" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="V97">
         <v>0</v>
@@ -8685,14 +8696,14 @@
       <c r="N98" t="s">
         <v>65</v>
       </c>
-      <c r="P98">
-        <v>5057805794608</v>
+      <c r="P98" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q98" t="s">
         <v>83</v>
       </c>
       <c r="R98" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="V98">
         <v>68</v>
@@ -8763,13 +8774,13 @@
         <v>65</v>
       </c>
       <c r="P99">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q99" t="s">
         <v>83</v>
       </c>
       <c r="R99" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="V99">
         <v>0</v>
@@ -8839,14 +8850,14 @@
       <c r="N100" t="s">
         <v>65</v>
       </c>
-      <c r="P100">
-        <v>5057805794608</v>
+      <c r="P100" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q100" t="s">
         <v>83</v>
       </c>
       <c r="R100" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="V100">
         <v>0</v>
@@ -8917,13 +8928,13 @@
         <v>65</v>
       </c>
       <c r="P101">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q101" t="s">
         <v>83</v>
       </c>
       <c r="R101" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="V101">
         <v>3</v>
@@ -8993,14 +9004,14 @@
       <c r="N102" t="s">
         <v>65</v>
       </c>
-      <c r="P102">
-        <v>5057805794608</v>
+      <c r="P102" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q102" t="s">
         <v>83</v>
       </c>
       <c r="R102" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="V102">
         <v>294</v>
@@ -9071,13 +9082,13 @@
         <v>65</v>
       </c>
       <c r="P103">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q103" t="s">
         <v>83</v>
       </c>
       <c r="R103" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="V103">
         <v>0</v>
@@ -9147,14 +9158,14 @@
       <c r="N104" t="s">
         <v>65</v>
       </c>
-      <c r="P104">
-        <v>5057805794608</v>
+      <c r="P104" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q104" t="s">
         <v>83</v>
       </c>
       <c r="R104" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="V104">
         <v>1</v>
@@ -9225,13 +9236,13 @@
         <v>65</v>
       </c>
       <c r="P105">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q105" t="s">
         <v>83</v>
       </c>
       <c r="R105" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="V105">
         <v>0</v>
@@ -9301,14 +9312,14 @@
       <c r="N106" t="s">
         <v>65</v>
       </c>
-      <c r="P106">
-        <v>5057805794608</v>
+      <c r="P106" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q106" t="s">
         <v>83</v>
       </c>
       <c r="R106" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="V106">
         <v>153</v>
@@ -9379,13 +9390,13 @@
         <v>65</v>
       </c>
       <c r="P107">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q107" t="s">
         <v>83</v>
       </c>
       <c r="R107" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="V107">
         <v>0</v>
@@ -9455,14 +9466,14 @@
       <c r="N108" t="s">
         <v>65</v>
       </c>
-      <c r="P108">
-        <v>5057805794608</v>
+      <c r="P108" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q108" t="s">
         <v>83</v>
       </c>
       <c r="R108" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="V108">
         <v>0</v>
@@ -9533,13 +9544,13 @@
         <v>65</v>
       </c>
       <c r="P109">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q109" t="s">
         <v>83</v>
       </c>
       <c r="R109" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="V109">
         <v>0</v>
@@ -9609,14 +9620,14 @@
       <c r="N110" t="s">
         <v>65</v>
       </c>
-      <c r="P110">
-        <v>5057805794608</v>
+      <c r="P110" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q110" t="s">
         <v>83</v>
       </c>
       <c r="R110" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="V110">
         <v>0</v>
@@ -9687,13 +9698,13 @@
         <v>65</v>
       </c>
       <c r="P111">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q111" t="s">
         <v>83</v>
       </c>
       <c r="R111" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="V111">
         <v>96</v>
@@ -9763,14 +9774,14 @@
       <c r="N112" t="s">
         <v>65</v>
       </c>
-      <c r="P112">
-        <v>5057805794608</v>
+      <c r="P112" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q112" t="s">
         <v>83</v>
       </c>
       <c r="R112" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="V112">
         <v>0</v>
@@ -9841,13 +9852,13 @@
         <v>65</v>
       </c>
       <c r="P113">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q113" t="s">
         <v>83</v>
       </c>
       <c r="R113" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="V113">
         <v>0</v>
@@ -9917,14 +9928,14 @@
       <c r="N114" t="s">
         <v>65</v>
       </c>
-      <c r="P114">
-        <v>5057805794608</v>
+      <c r="P114" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q114" t="s">
         <v>83</v>
       </c>
       <c r="R114" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="V114">
         <v>0</v>
@@ -9995,13 +10006,13 @@
         <v>65</v>
       </c>
       <c r="P115">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q115" t="s">
         <v>83</v>
       </c>
       <c r="R115" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="V115">
         <v>0</v>
@@ -10071,14 +10082,14 @@
       <c r="N116" t="s">
         <v>65</v>
       </c>
-      <c r="P116">
-        <v>5057805794608</v>
+      <c r="P116" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q116" t="s">
         <v>83</v>
       </c>
       <c r="R116" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="V116">
         <v>0</v>
@@ -10149,13 +10160,13 @@
         <v>65</v>
       </c>
       <c r="P117">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q117" t="s">
         <v>83</v>
       </c>
       <c r="R117" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="V117">
         <v>0</v>
@@ -10225,14 +10236,14 @@
       <c r="N118" t="s">
         <v>65</v>
       </c>
-      <c r="P118">
-        <v>5057805794608</v>
+      <c r="P118" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q118" t="s">
         <v>83</v>
       </c>
       <c r="R118" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="V118">
         <v>0</v>
@@ -10303,13 +10314,13 @@
         <v>65</v>
       </c>
       <c r="P119">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q119" t="s">
         <v>83</v>
       </c>
       <c r="R119" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="V119">
         <v>0</v>
@@ -10379,14 +10390,14 @@
       <c r="N120" t="s">
         <v>65</v>
       </c>
-      <c r="P120">
-        <v>5057805794608</v>
+      <c r="P120" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q120" t="s">
         <v>83</v>
       </c>
       <c r="R120" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="V120">
         <v>0</v>
@@ -10457,13 +10468,13 @@
         <v>65</v>
       </c>
       <c r="P121">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q121" t="s">
         <v>83</v>
       </c>
       <c r="R121" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="V121">
         <v>0</v>
@@ -10533,14 +10544,14 @@
       <c r="N122" t="s">
         <v>65</v>
       </c>
-      <c r="P122">
-        <v>5057805794608</v>
+      <c r="P122" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q122" t="s">
         <v>83</v>
       </c>
       <c r="R122" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="V122">
         <v>0</v>
@@ -10611,13 +10622,13 @@
         <v>65</v>
       </c>
       <c r="P123">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q123" t="s">
         <v>83</v>
       </c>
       <c r="R123" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="V123">
         <v>2</v>
@@ -10687,14 +10698,14 @@
       <c r="N124" t="s">
         <v>65</v>
       </c>
-      <c r="P124">
-        <v>5057805794608</v>
+      <c r="P124" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q124" t="s">
         <v>83</v>
       </c>
       <c r="R124" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="V124">
         <v>0</v>
@@ -10765,13 +10776,13 @@
         <v>65</v>
       </c>
       <c r="P125">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q125" t="s">
         <v>83</v>
       </c>
       <c r="R125" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="V125">
         <v>0</v>
@@ -10841,14 +10852,14 @@
       <c r="N126" t="s">
         <v>65</v>
       </c>
-      <c r="P126">
-        <v>5057805794608</v>
+      <c r="P126" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q126" t="s">
         <v>83</v>
       </c>
       <c r="R126" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="V126">
         <v>0</v>
@@ -10919,13 +10930,13 @@
         <v>65</v>
       </c>
       <c r="P127">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q127" t="s">
         <v>83</v>
       </c>
       <c r="R127" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="V127">
         <v>0</v>
@@ -10995,14 +11006,14 @@
       <c r="N128" t="s">
         <v>65</v>
       </c>
-      <c r="P128">
-        <v>5057805794608</v>
+      <c r="P128" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q128" t="s">
         <v>83</v>
       </c>
       <c r="R128" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="V128">
         <v>0</v>
@@ -11073,13 +11084,13 @@
         <v>65</v>
       </c>
       <c r="P129">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q129" t="s">
         <v>83</v>
       </c>
       <c r="R129" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="V129">
         <v>0</v>
@@ -11149,14 +11160,14 @@
       <c r="N130" t="s">
         <v>65</v>
       </c>
-      <c r="P130">
-        <v>5057805794608</v>
+      <c r="P130" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q130" t="s">
         <v>83</v>
       </c>
       <c r="R130" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="V130">
         <v>0</v>
@@ -11227,13 +11238,13 @@
         <v>65</v>
       </c>
       <c r="P131">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q131" t="s">
         <v>83</v>
       </c>
       <c r="R131" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="V131">
         <v>0</v>
@@ -11303,14 +11314,14 @@
       <c r="N132" t="s">
         <v>65</v>
       </c>
-      <c r="P132">
-        <v>5057805794608</v>
+      <c r="P132" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q132" t="s">
         <v>83</v>
       </c>
       <c r="R132" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="V132">
         <v>0</v>
@@ -11381,13 +11392,13 @@
         <v>65</v>
       </c>
       <c r="P133">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q133" t="s">
         <v>83</v>
       </c>
       <c r="R133" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="V133">
         <v>0</v>
@@ -11457,14 +11468,14 @@
       <c r="N134" t="s">
         <v>65</v>
       </c>
-      <c r="P134">
-        <v>5057805794608</v>
+      <c r="P134" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q134" t="s">
         <v>83</v>
       </c>
       <c r="R134" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="V134">
         <v>0</v>
@@ -11535,13 +11546,13 @@
         <v>65</v>
       </c>
       <c r="P135">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q135" t="s">
         <v>83</v>
       </c>
       <c r="R135" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="V135">
         <v>0</v>
@@ -11611,14 +11622,14 @@
       <c r="N136" t="s">
         <v>65</v>
       </c>
-      <c r="P136">
-        <v>5057805794608</v>
+      <c r="P136" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q136" t="s">
         <v>83</v>
       </c>
       <c r="R136" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="V136">
         <v>0</v>
@@ -11689,13 +11700,13 @@
         <v>65</v>
       </c>
       <c r="P137">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q137" t="s">
         <v>83</v>
       </c>
       <c r="R137" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="V137">
         <v>0</v>
@@ -11765,14 +11776,14 @@
       <c r="N138" t="s">
         <v>65</v>
       </c>
-      <c r="P138">
-        <v>5057805794608</v>
+      <c r="P138" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q138" t="s">
         <v>83</v>
       </c>
       <c r="R138" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="V138">
         <v>0</v>
@@ -11843,13 +11854,13 @@
         <v>65</v>
       </c>
       <c r="P139">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q139" t="s">
         <v>83</v>
       </c>
       <c r="R139" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="V139">
         <v>20</v>
@@ -11919,14 +11930,14 @@
       <c r="N140" t="s">
         <v>65</v>
       </c>
-      <c r="P140">
-        <v>5057805794608</v>
+      <c r="P140" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q140" t="s">
         <v>83</v>
       </c>
       <c r="R140" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="V140">
         <v>0</v>
@@ -11997,13 +12008,13 @@
         <v>65</v>
       </c>
       <c r="P141">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q141" t="s">
         <v>83</v>
       </c>
       <c r="R141" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="V141">
         <v>0</v>
@@ -12073,14 +12084,14 @@
       <c r="N142" t="s">
         <v>65</v>
       </c>
-      <c r="P142">
-        <v>5057805794608</v>
+      <c r="P142" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q142" t="s">
         <v>83</v>
       </c>
       <c r="R142" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="V142">
         <v>0</v>
@@ -12151,13 +12162,13 @@
         <v>65</v>
       </c>
       <c r="P143">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q143" t="s">
         <v>83</v>
       </c>
       <c r="R143" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="V143">
         <v>0</v>
@@ -12227,14 +12238,14 @@
       <c r="N144" t="s">
         <v>65</v>
       </c>
-      <c r="P144">
-        <v>5057805794608</v>
+      <c r="P144" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q144" t="s">
         <v>83</v>
       </c>
       <c r="R144" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="V144">
         <v>0</v>
@@ -12305,13 +12316,13 @@
         <v>65</v>
       </c>
       <c r="P145">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q145" t="s">
         <v>83</v>
       </c>
       <c r="R145" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="V145">
         <v>0</v>
@@ -12381,14 +12392,14 @@
       <c r="N146" t="s">
         <v>65</v>
       </c>
-      <c r="P146">
-        <v>5057805794608</v>
+      <c r="P146" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q146" t="s">
         <v>83</v>
       </c>
       <c r="R146" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="V146">
         <v>323</v>
@@ -12459,13 +12470,13 @@
         <v>65</v>
       </c>
       <c r="P147">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q147" t="s">
         <v>83</v>
       </c>
       <c r="R147" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="V147">
         <v>0</v>
@@ -12535,14 +12546,14 @@
       <c r="N148" t="s">
         <v>65</v>
       </c>
-      <c r="P148">
-        <v>5057805794608</v>
+      <c r="P148" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q148" t="s">
         <v>83</v>
       </c>
       <c r="R148" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="V148">
         <v>0</v>
@@ -12613,13 +12624,13 @@
         <v>65</v>
       </c>
       <c r="P149">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q149" t="s">
         <v>83</v>
       </c>
       <c r="R149" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="V149">
         <v>0</v>
@@ -12689,14 +12700,14 @@
       <c r="N150" t="s">
         <v>65</v>
       </c>
-      <c r="P150">
-        <v>5057805794608</v>
+      <c r="P150" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q150" t="s">
         <v>83</v>
       </c>
       <c r="R150" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="V150">
         <v>0</v>
@@ -12767,13 +12778,13 @@
         <v>65</v>
       </c>
       <c r="P151">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q151" t="s">
         <v>83</v>
       </c>
       <c r="R151" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="V151">
         <v>0</v>
@@ -12843,14 +12854,14 @@
       <c r="N152" t="s">
         <v>65</v>
       </c>
-      <c r="P152">
-        <v>5057805794608</v>
+      <c r="P152" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q152" t="s">
         <v>83</v>
       </c>
       <c r="R152" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="V152">
         <v>0</v>
@@ -12921,13 +12932,13 @@
         <v>65</v>
       </c>
       <c r="P153">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q153" t="s">
         <v>83</v>
       </c>
       <c r="R153" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="V153">
         <v>0</v>
@@ -12997,14 +13008,14 @@
       <c r="N154" t="s">
         <v>65</v>
       </c>
-      <c r="P154">
-        <v>5057805794608</v>
+      <c r="P154" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q154" t="s">
         <v>83</v>
       </c>
       <c r="R154" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="V154">
         <v>0</v>
@@ -13075,13 +13086,13 @@
         <v>65</v>
       </c>
       <c r="P155">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q155" t="s">
         <v>83</v>
       </c>
       <c r="R155" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="V155">
         <v>0</v>
@@ -13151,14 +13162,14 @@
       <c r="N156" t="s">
         <v>65</v>
       </c>
-      <c r="P156">
-        <v>5057805794608</v>
+      <c r="P156" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q156" t="s">
         <v>83</v>
       </c>
       <c r="R156" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="V156">
         <v>0</v>
@@ -13229,13 +13240,13 @@
         <v>65</v>
       </c>
       <c r="P157">
-        <v>5057805794608</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q157" t="s">
         <v>83</v>
       </c>
       <c r="R157" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="V157">
         <v>0</v>
@@ -13305,14 +13316,14 @@
       <c r="N158" t="s">
         <v>65</v>
       </c>
-      <c r="P158">
-        <v>5057805794608</v>
+      <c r="P158" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q158" t="s">
         <v>83</v>
       </c>
       <c r="R158" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="V158">
         <v>0</v>
@@ -13386,16 +13397,16 @@
         <v>184</v>
       </c>
       <c r="P159">
-        <v>5057805794653</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q159" t="s">
         <v>185</v>
       </c>
       <c r="R159" t="s">
+        <v>202</v>
+      </c>
+      <c r="S159" t="s">
         <v>186</v>
-      </c>
-      <c r="S159" t="s">
-        <v>187</v>
       </c>
       <c r="V159">
         <v>1</v>
@@ -13471,14 +13482,14 @@
       <c r="N160" t="s">
         <v>65</v>
       </c>
-      <c r="P160">
-        <v>5057805794653</v>
+      <c r="P160" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q160" t="s">
         <v>185</v>
       </c>
       <c r="R160" t="s">
-        <v>186</v>
+        <v>202</v>
       </c>
       <c r="V160">
         <v>0</v>
@@ -13519,7 +13530,7 @@
         <v>60</v>
       </c>
       <c r="B161" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C161" s="2">
         <v>44743</v>
@@ -13534,34 +13545,34 @@
         <v>1.2002340330000001</v>
       </c>
       <c r="G161" t="s">
+        <v>188</v>
+      </c>
+      <c r="I161" t="s">
         <v>189</v>
       </c>
-      <c r="I161" t="s">
+      <c r="K161" t="s">
+        <v>189</v>
+      </c>
+      <c r="L161">
+        <v>1</v>
+      </c>
+      <c r="N161" t="s">
+        <v>65</v>
+      </c>
+      <c r="O161" t="s">
         <v>190</v>
       </c>
-      <c r="K161" t="s">
-        <v>190</v>
-      </c>
-      <c r="L161">
-        <v>1</v>
-      </c>
-      <c r="N161" t="s">
-        <v>65</v>
-      </c>
-      <c r="O161" t="s">
+      <c r="P161">
+        <v>5057805794592</v>
+      </c>
+      <c r="Q161" t="s">
         <v>191</v>
       </c>
-      <c r="P161">
-        <v>5057805794660</v>
-      </c>
-      <c r="Q161" t="s">
+      <c r="R161" t="s">
+        <v>202</v>
+      </c>
+      <c r="S161" t="s">
         <v>192</v>
-      </c>
-      <c r="R161" t="s">
-        <v>193</v>
-      </c>
-      <c r="S161" t="s">
-        <v>194</v>
       </c>
       <c r="V161">
         <v>2</v>
@@ -13602,7 +13613,7 @@
         <v>60</v>
       </c>
       <c r="B162" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C162" s="2">
         <v>44743</v>
@@ -13617,34 +13628,34 @@
         <v>1.2002340330000001</v>
       </c>
       <c r="G162" t="s">
+        <v>188</v>
+      </c>
+      <c r="I162" t="s">
         <v>189</v>
       </c>
-      <c r="I162" t="s">
+      <c r="K162" t="s">
+        <v>189</v>
+      </c>
+      <c r="L162">
+        <v>1</v>
+      </c>
+      <c r="N162" t="s">
+        <v>65</v>
+      </c>
+      <c r="O162" t="s">
         <v>190</v>
       </c>
-      <c r="K162" t="s">
-        <v>190</v>
-      </c>
-      <c r="L162">
-        <v>1</v>
-      </c>
-      <c r="N162" t="s">
-        <v>65</v>
-      </c>
-      <c r="O162" t="s">
+      <c r="P162" s="5">
+        <v>5057805794592</v>
+      </c>
+      <c r="Q162" t="s">
         <v>191</v>
       </c>
-      <c r="P162">
-        <v>5057805794660</v>
-      </c>
-      <c r="Q162" t="s">
+      <c r="R162" t="s">
+        <v>202</v>
+      </c>
+      <c r="S162" t="s">
         <v>192</v>
-      </c>
-      <c r="R162" t="s">
-        <v>193</v>
-      </c>
-      <c r="S162" t="s">
-        <v>194</v>
       </c>
       <c r="V162">
         <v>1</v>
@@ -13700,34 +13711,34 @@
         <v>1.200234016</v>
       </c>
       <c r="G163" t="s">
+        <v>188</v>
+      </c>
+      <c r="I163" t="s">
         <v>189</v>
       </c>
-      <c r="I163" t="s">
+      <c r="K163" t="s">
+        <v>189</v>
+      </c>
+      <c r="L163">
+        <v>1</v>
+      </c>
+      <c r="N163" t="s">
+        <v>65</v>
+      </c>
+      <c r="O163" t="s">
         <v>190</v>
       </c>
-      <c r="K163" t="s">
-        <v>190</v>
-      </c>
-      <c r="L163">
-        <v>1</v>
-      </c>
-      <c r="N163" t="s">
-        <v>65</v>
-      </c>
-      <c r="O163" t="s">
+      <c r="P163">
+        <v>5057805794592</v>
+      </c>
+      <c r="Q163" t="s">
         <v>191</v>
       </c>
-      <c r="P163">
-        <v>5057805794660</v>
-      </c>
-      <c r="Q163" t="s">
+      <c r="R163" t="s">
+        <v>202</v>
+      </c>
+      <c r="S163" t="s">
         <v>192</v>
-      </c>
-      <c r="R163" t="s">
-        <v>193</v>
-      </c>
-      <c r="S163" t="s">
-        <v>194</v>
       </c>
       <c r="V163">
         <v>5</v>
@@ -13768,7 +13779,7 @@
         <v>60</v>
       </c>
       <c r="B164" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C164" s="2">
         <v>44743</v>
@@ -13783,34 +13794,34 @@
         <v>1.2002340330000001</v>
       </c>
       <c r="G164" t="s">
+        <v>188</v>
+      </c>
+      <c r="I164" t="s">
         <v>189</v>
       </c>
-      <c r="I164" t="s">
+      <c r="K164" t="s">
+        <v>189</v>
+      </c>
+      <c r="L164">
+        <v>1</v>
+      </c>
+      <c r="N164" t="s">
+        <v>65</v>
+      </c>
+      <c r="O164" t="s">
         <v>190</v>
       </c>
-      <c r="K164" t="s">
-        <v>190</v>
-      </c>
-      <c r="L164">
-        <v>1</v>
-      </c>
-      <c r="N164" t="s">
-        <v>65</v>
-      </c>
-      <c r="O164" t="s">
+      <c r="P164" s="5">
+        <v>5057805794592</v>
+      </c>
+      <c r="Q164" t="s">
         <v>191</v>
       </c>
-      <c r="P164">
-        <v>5057805794660</v>
-      </c>
-      <c r="Q164" t="s">
+      <c r="R164" t="s">
+        <v>202</v>
+      </c>
+      <c r="S164" t="s">
         <v>192</v>
-      </c>
-      <c r="R164" t="s">
-        <v>193</v>
-      </c>
-      <c r="S164" t="s">
-        <v>194</v>
       </c>
       <c r="V164">
         <v>2</v>
@@ -13851,7 +13862,7 @@
         <v>60</v>
       </c>
       <c r="B165" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C165" s="2">
         <v>44743</v>
@@ -13866,34 +13877,34 @@
         <v>1.2002340330000001</v>
       </c>
       <c r="G165" t="s">
+        <v>188</v>
+      </c>
+      <c r="I165" t="s">
         <v>189</v>
       </c>
-      <c r="I165" t="s">
+      <c r="K165" t="s">
+        <v>189</v>
+      </c>
+      <c r="L165">
+        <v>1</v>
+      </c>
+      <c r="N165" t="s">
+        <v>65</v>
+      </c>
+      <c r="O165" t="s">
         <v>190</v>
       </c>
-      <c r="K165" t="s">
-        <v>190</v>
-      </c>
-      <c r="L165">
-        <v>1</v>
-      </c>
-      <c r="N165" t="s">
-        <v>65</v>
-      </c>
-      <c r="O165" t="s">
+      <c r="P165">
+        <v>5057805794592</v>
+      </c>
+      <c r="Q165" t="s">
         <v>191</v>
       </c>
-      <c r="P165">
-        <v>5057805794660</v>
-      </c>
-      <c r="Q165" t="s">
+      <c r="R165" t="s">
+        <v>202</v>
+      </c>
+      <c r="S165" t="s">
         <v>192</v>
-      </c>
-      <c r="R165" t="s">
-        <v>193</v>
-      </c>
-      <c r="S165" t="s">
-        <v>194</v>
       </c>
       <c r="V165">
         <v>1</v>
@@ -13949,43 +13960,43 @@
         <v>1.200234016</v>
       </c>
       <c r="G166" t="s">
+        <v>188</v>
+      </c>
+      <c r="I166" t="s">
         <v>189</v>
       </c>
-      <c r="I166" t="s">
+      <c r="K166" t="s">
+        <v>189</v>
+      </c>
+      <c r="L166">
+        <v>1</v>
+      </c>
+      <c r="N166" t="s">
+        <v>65</v>
+      </c>
+      <c r="O166" t="s">
         <v>190</v>
       </c>
-      <c r="K166" t="s">
-        <v>190</v>
-      </c>
-      <c r="L166">
-        <v>1</v>
-      </c>
-      <c r="N166" t="s">
-        <v>65</v>
-      </c>
-      <c r="O166" t="s">
+      <c r="P166" s="5">
+        <v>5057805794592</v>
+      </c>
+      <c r="Q166" t="s">
         <v>191</v>
       </c>
-      <c r="P166">
-        <v>5057805794660</v>
-      </c>
-      <c r="Q166" t="s">
+      <c r="R166" t="s">
+        <v>202</v>
+      </c>
+      <c r="S166" t="s">
         <v>192</v>
       </c>
-      <c r="R166" t="s">
+      <c r="V166">
+        <v>1</v>
+      </c>
+      <c r="W166" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y166" t="s">
         <v>193</v>
-      </c>
-      <c r="S166" t="s">
-        <v>194</v>
-      </c>
-      <c r="V166">
-        <v>1</v>
-      </c>
-      <c r="W166" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y166" t="s">
-        <v>195</v>
       </c>
       <c r="AB166">
         <v>1</v>
@@ -14032,34 +14043,34 @@
         <v>1.200234016</v>
       </c>
       <c r="G167" t="s">
+        <v>188</v>
+      </c>
+      <c r="I167" t="s">
         <v>189</v>
       </c>
-      <c r="I167" t="s">
+      <c r="K167" t="s">
+        <v>189</v>
+      </c>
+      <c r="L167">
+        <v>1</v>
+      </c>
+      <c r="N167" t="s">
+        <v>65</v>
+      </c>
+      <c r="O167" t="s">
         <v>190</v>
       </c>
-      <c r="K167" t="s">
-        <v>190</v>
-      </c>
-      <c r="L167">
-        <v>1</v>
-      </c>
-      <c r="N167" t="s">
-        <v>65</v>
-      </c>
-      <c r="O167" t="s">
+      <c r="P167">
+        <v>5057805794592</v>
+      </c>
+      <c r="Q167" t="s">
         <v>191</v>
       </c>
-      <c r="P167">
-        <v>5057805794660</v>
-      </c>
-      <c r="Q167" t="s">
+      <c r="R167" t="s">
+        <v>202</v>
+      </c>
+      <c r="S167" t="s">
         <v>192</v>
-      </c>
-      <c r="R167" t="s">
-        <v>193</v>
-      </c>
-      <c r="S167" t="s">
-        <v>194</v>
       </c>
       <c r="V167">
         <v>4</v>
@@ -14100,7 +14111,7 @@
         <v>60</v>
       </c>
       <c r="B168" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C168" s="2">
         <v>44743</v>
@@ -14115,34 +14126,34 @@
         <v>1.2002340330000001</v>
       </c>
       <c r="G168" t="s">
+        <v>188</v>
+      </c>
+      <c r="I168" t="s">
         <v>189</v>
       </c>
-      <c r="I168" t="s">
+      <c r="K168" t="s">
+        <v>189</v>
+      </c>
+      <c r="L168">
+        <v>1</v>
+      </c>
+      <c r="N168" t="s">
+        <v>65</v>
+      </c>
+      <c r="O168" t="s">
         <v>190</v>
       </c>
-      <c r="K168" t="s">
-        <v>190</v>
-      </c>
-      <c r="L168">
-        <v>1</v>
-      </c>
-      <c r="N168" t="s">
-        <v>65</v>
-      </c>
-      <c r="O168" t="s">
+      <c r="P168" s="5">
+        <v>5057805794592</v>
+      </c>
+      <c r="Q168" t="s">
         <v>191</v>
       </c>
-      <c r="P168">
-        <v>5057805794660</v>
-      </c>
-      <c r="Q168" t="s">
+      <c r="R168" t="s">
+        <v>202</v>
+      </c>
+      <c r="S168" t="s">
         <v>192</v>
-      </c>
-      <c r="R168" t="s">
-        <v>193</v>
-      </c>
-      <c r="S168" t="s">
-        <v>194</v>
       </c>
       <c r="V168">
         <v>3</v>
@@ -14183,7 +14194,7 @@
         <v>60</v>
       </c>
       <c r="B169" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C169" s="2">
         <v>44743</v>
@@ -14198,34 +14209,34 @@
         <v>1.2002340330000001</v>
       </c>
       <c r="G169" t="s">
+        <v>188</v>
+      </c>
+      <c r="I169" t="s">
         <v>189</v>
       </c>
-      <c r="I169" t="s">
+      <c r="K169" t="s">
+        <v>189</v>
+      </c>
+      <c r="L169">
+        <v>1</v>
+      </c>
+      <c r="N169" t="s">
+        <v>65</v>
+      </c>
+      <c r="O169" t="s">
         <v>190</v>
       </c>
-      <c r="K169" t="s">
-        <v>190</v>
-      </c>
-      <c r="L169">
-        <v>1</v>
-      </c>
-      <c r="N169" t="s">
-        <v>65</v>
-      </c>
-      <c r="O169" t="s">
+      <c r="P169">
+        <v>5057805794592</v>
+      </c>
+      <c r="Q169" t="s">
         <v>191</v>
       </c>
-      <c r="P169">
-        <v>5057805794660</v>
-      </c>
-      <c r="Q169" t="s">
+      <c r="R169" t="s">
+        <v>202</v>
+      </c>
+      <c r="S169" t="s">
         <v>192</v>
-      </c>
-      <c r="R169" t="s">
-        <v>193</v>
-      </c>
-      <c r="S169" t="s">
-        <v>194</v>
       </c>
       <c r="V169">
         <v>1</v>
@@ -14281,34 +14292,34 @@
         <v>1.200234016</v>
       </c>
       <c r="G170" t="s">
+        <v>188</v>
+      </c>
+      <c r="I170" t="s">
         <v>189</v>
       </c>
-      <c r="I170" t="s">
+      <c r="K170" t="s">
+        <v>189</v>
+      </c>
+      <c r="L170">
+        <v>1</v>
+      </c>
+      <c r="N170" t="s">
+        <v>65</v>
+      </c>
+      <c r="O170" t="s">
         <v>190</v>
       </c>
-      <c r="K170" t="s">
-        <v>190</v>
-      </c>
-      <c r="L170">
-        <v>1</v>
-      </c>
-      <c r="N170" t="s">
-        <v>65</v>
-      </c>
-      <c r="O170" t="s">
+      <c r="P170" s="5">
+        <v>5057805794592</v>
+      </c>
+      <c r="Q170" t="s">
         <v>191</v>
       </c>
-      <c r="P170">
-        <v>5057805794660</v>
-      </c>
-      <c r="Q170" t="s">
+      <c r="R170" t="s">
+        <v>202</v>
+      </c>
+      <c r="S170" t="s">
         <v>192</v>
-      </c>
-      <c r="R170" t="s">
-        <v>193</v>
-      </c>
-      <c r="S170" t="s">
-        <v>194</v>
       </c>
       <c r="V170">
         <v>3</v>
@@ -14349,7 +14360,7 @@
         <v>60</v>
       </c>
       <c r="B171" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C171" s="2">
         <v>44743</v>
@@ -14364,34 +14375,34 @@
         <v>1.2002340330000001</v>
       </c>
       <c r="G171" t="s">
+        <v>188</v>
+      </c>
+      <c r="I171" t="s">
         <v>189</v>
       </c>
-      <c r="I171" t="s">
+      <c r="K171" t="s">
+        <v>189</v>
+      </c>
+      <c r="L171">
+        <v>1</v>
+      </c>
+      <c r="N171" t="s">
+        <v>65</v>
+      </c>
+      <c r="O171" t="s">
         <v>190</v>
       </c>
-      <c r="K171" t="s">
-        <v>190</v>
-      </c>
-      <c r="L171">
-        <v>1</v>
-      </c>
-      <c r="N171" t="s">
-        <v>65</v>
-      </c>
-      <c r="O171" t="s">
+      <c r="P171">
+        <v>5057805794592</v>
+      </c>
+      <c r="Q171" t="s">
         <v>191</v>
       </c>
-      <c r="P171">
-        <v>5057805794660</v>
-      </c>
-      <c r="Q171" t="s">
+      <c r="R171" t="s">
+        <v>202</v>
+      </c>
+      <c r="S171" t="s">
         <v>192</v>
-      </c>
-      <c r="R171" t="s">
-        <v>193</v>
-      </c>
-      <c r="S171" t="s">
-        <v>194</v>
       </c>
       <c r="V171">
         <v>2</v>
@@ -14447,16 +14458,16 @@
         <v>1.1422334949999999</v>
       </c>
       <c r="G172" t="s">
+        <v>188</v>
+      </c>
+      <c r="I172" t="s">
         <v>189</v>
       </c>
-      <c r="I172" t="s">
-        <v>190</v>
-      </c>
       <c r="J172" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="K172" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L172">
         <v>1</v>
@@ -14467,14 +14478,14 @@
       <c r="N172" t="s">
         <v>65</v>
       </c>
-      <c r="P172">
-        <v>5057805794660</v>
+      <c r="P172" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q172" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="R172" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="V172">
         <v>0</v>
@@ -14515,7 +14526,7 @@
         <v>60</v>
       </c>
       <c r="B173" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C173" s="2">
         <v>44743</v>
@@ -14530,34 +14541,34 @@
         <v>1.2002340330000001</v>
       </c>
       <c r="G173" t="s">
+        <v>188</v>
+      </c>
+      <c r="I173" t="s">
         <v>189</v>
       </c>
-      <c r="I173" t="s">
+      <c r="K173" t="s">
+        <v>189</v>
+      </c>
+      <c r="L173">
+        <v>1</v>
+      </c>
+      <c r="N173" t="s">
+        <v>65</v>
+      </c>
+      <c r="O173" t="s">
         <v>190</v>
       </c>
-      <c r="K173" t="s">
-        <v>190</v>
-      </c>
-      <c r="L173">
-        <v>1</v>
-      </c>
-      <c r="N173" t="s">
-        <v>65</v>
-      </c>
-      <c r="O173" t="s">
+      <c r="P173">
+        <v>5057805794592</v>
+      </c>
+      <c r="Q173" t="s">
         <v>191</v>
       </c>
-      <c r="P173">
-        <v>5057805794660</v>
-      </c>
-      <c r="Q173" t="s">
+      <c r="R173" t="s">
+        <v>202</v>
+      </c>
+      <c r="S173" t="s">
         <v>192</v>
-      </c>
-      <c r="R173" t="s">
-        <v>193</v>
-      </c>
-      <c r="S173" t="s">
-        <v>194</v>
       </c>
       <c r="V173">
         <v>7</v>
@@ -14566,7 +14577,7 @@
         <v>69</v>
       </c>
       <c r="Y173" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="AB173">
         <v>7</v>
@@ -14598,7 +14609,7 @@
         <v>60</v>
       </c>
       <c r="B174" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C174" s="2">
         <v>44713</v>
@@ -14607,22 +14618,22 @@
         <v>44742</v>
       </c>
       <c r="E174" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F174" s="3">
         <v>1.189137245</v>
       </c>
       <c r="G174" t="s">
+        <v>188</v>
+      </c>
+      <c r="I174" t="s">
         <v>189</v>
       </c>
-      <c r="I174" t="s">
-        <v>190</v>
-      </c>
       <c r="J174" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="K174" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L174">
         <v>1</v>
@@ -14633,14 +14644,14 @@
       <c r="N174" t="s">
         <v>65</v>
       </c>
-      <c r="P174">
-        <v>5057805794660</v>
+      <c r="P174" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q174" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="R174" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="V174">
         <v>1</v>
@@ -14658,7 +14669,7 @@
         <v>76</v>
       </c>
       <c r="AF174" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="BR174" t="s">
         <v>72</v>
@@ -14684,7 +14695,7 @@
         <v>60</v>
       </c>
       <c r="B175" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C175" s="2">
         <v>44743</v>
@@ -14699,43 +14710,43 @@
         <v>1.2002340330000001</v>
       </c>
       <c r="G175" t="s">
+        <v>188</v>
+      </c>
+      <c r="I175" t="s">
         <v>189</v>
       </c>
-      <c r="I175" t="s">
+      <c r="K175" t="s">
+        <v>189</v>
+      </c>
+      <c r="L175">
+        <v>1</v>
+      </c>
+      <c r="N175" t="s">
+        <v>65</v>
+      </c>
+      <c r="O175" t="s">
         <v>190</v>
       </c>
-      <c r="K175" t="s">
-        <v>190</v>
-      </c>
-      <c r="L175">
-        <v>1</v>
-      </c>
-      <c r="N175" t="s">
-        <v>65</v>
-      </c>
-      <c r="O175" t="s">
+      <c r="P175">
+        <v>5057805794592</v>
+      </c>
+      <c r="Q175" t="s">
         <v>191</v>
       </c>
-      <c r="P175">
-        <v>5057805794660</v>
-      </c>
-      <c r="Q175" t="s">
+      <c r="R175" t="s">
+        <v>202</v>
+      </c>
+      <c r="S175" t="s">
         <v>192</v>
       </c>
-      <c r="R175" t="s">
-        <v>193</v>
-      </c>
-      <c r="S175" t="s">
+      <c r="V175">
+        <v>1</v>
+      </c>
+      <c r="W175" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y175" t="s">
         <v>194</v>
-      </c>
-      <c r="V175">
-        <v>1</v>
-      </c>
-      <c r="W175" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y175" t="s">
-        <v>196</v>
       </c>
       <c r="AB175">
         <v>1</v>
@@ -14767,7 +14778,7 @@
         <v>60</v>
       </c>
       <c r="B176" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C176" s="2">
         <v>44743</v>
@@ -14782,34 +14793,34 @@
         <v>1.2002340330000001</v>
       </c>
       <c r="G176" t="s">
+        <v>188</v>
+      </c>
+      <c r="I176" t="s">
         <v>189</v>
       </c>
-      <c r="I176" t="s">
+      <c r="K176" t="s">
+        <v>189</v>
+      </c>
+      <c r="L176">
+        <v>1</v>
+      </c>
+      <c r="N176" t="s">
+        <v>65</v>
+      </c>
+      <c r="O176" t="s">
         <v>190</v>
       </c>
-      <c r="K176" t="s">
-        <v>190</v>
-      </c>
-      <c r="L176">
-        <v>1</v>
-      </c>
-      <c r="N176" t="s">
-        <v>65</v>
-      </c>
-      <c r="O176" t="s">
+      <c r="P176" s="5">
+        <v>5057805794592</v>
+      </c>
+      <c r="Q176" t="s">
         <v>191</v>
       </c>
-      <c r="P176">
-        <v>5057805794660</v>
-      </c>
-      <c r="Q176" t="s">
+      <c r="R176" t="s">
+        <v>202</v>
+      </c>
+      <c r="S176" t="s">
         <v>192</v>
-      </c>
-      <c r="R176" t="s">
-        <v>193</v>
-      </c>
-      <c r="S176" t="s">
-        <v>194</v>
       </c>
       <c r="V176">
         <v>2</v>
@@ -14818,7 +14829,7 @@
         <v>69</v>
       </c>
       <c r="Y176" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="AB176">
         <v>2</v>
@@ -14865,34 +14876,34 @@
         <v>1.200234016</v>
       </c>
       <c r="G177" t="s">
+        <v>188</v>
+      </c>
+      <c r="I177" t="s">
         <v>189</v>
       </c>
-      <c r="I177" t="s">
+      <c r="K177" t="s">
+        <v>189</v>
+      </c>
+      <c r="L177">
+        <v>1</v>
+      </c>
+      <c r="N177" t="s">
+        <v>65</v>
+      </c>
+      <c r="O177" t="s">
         <v>190</v>
       </c>
-      <c r="K177" t="s">
-        <v>190</v>
-      </c>
-      <c r="L177">
-        <v>1</v>
-      </c>
-      <c r="N177" t="s">
-        <v>65</v>
-      </c>
-      <c r="O177" t="s">
+      <c r="P177">
+        <v>5057805794592</v>
+      </c>
+      <c r="Q177" t="s">
         <v>191</v>
       </c>
-      <c r="P177">
-        <v>5057805794660</v>
-      </c>
-      <c r="Q177" t="s">
+      <c r="R177" t="s">
+        <v>202</v>
+      </c>
+      <c r="S177" t="s">
         <v>192</v>
-      </c>
-      <c r="R177" t="s">
-        <v>193</v>
-      </c>
-      <c r="S177" t="s">
-        <v>194</v>
       </c>
       <c r="V177">
         <v>4</v>
@@ -14933,7 +14944,7 @@
         <v>60</v>
       </c>
       <c r="B178" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C178" s="2">
         <v>44713</v>
@@ -14942,22 +14953,22 @@
         <v>44742</v>
       </c>
       <c r="E178" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F178" s="3">
         <v>1.189137245</v>
       </c>
       <c r="G178" t="s">
+        <v>188</v>
+      </c>
+      <c r="I178" t="s">
         <v>189</v>
       </c>
-      <c r="I178" t="s">
-        <v>190</v>
-      </c>
       <c r="J178" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="K178" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L178">
         <v>1</v>
@@ -14968,14 +14979,14 @@
       <c r="N178" t="s">
         <v>65</v>
       </c>
-      <c r="P178">
-        <v>5057805794660</v>
+      <c r="P178" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q178" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="R178" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="V178">
         <v>5</v>
@@ -14993,7 +15004,7 @@
         <v>76</v>
       </c>
       <c r="AF178" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="BR178" t="s">
         <v>72</v>
@@ -15019,7 +15030,7 @@
         <v>60</v>
       </c>
       <c r="B179" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C179" s="2">
         <v>44743</v>
@@ -15034,34 +15045,34 @@
         <v>1.2002340330000001</v>
       </c>
       <c r="G179" t="s">
+        <v>188</v>
+      </c>
+      <c r="I179" t="s">
         <v>189</v>
       </c>
-      <c r="I179" t="s">
+      <c r="K179" t="s">
+        <v>189</v>
+      </c>
+      <c r="L179">
+        <v>1</v>
+      </c>
+      <c r="N179" t="s">
+        <v>65</v>
+      </c>
+      <c r="O179" t="s">
         <v>190</v>
       </c>
-      <c r="K179" t="s">
-        <v>190</v>
-      </c>
-      <c r="L179">
-        <v>1</v>
-      </c>
-      <c r="N179" t="s">
-        <v>65</v>
-      </c>
-      <c r="O179" t="s">
+      <c r="P179">
+        <v>5057805794592</v>
+      </c>
+      <c r="Q179" t="s">
         <v>191</v>
       </c>
-      <c r="P179">
-        <v>5057805794660</v>
-      </c>
-      <c r="Q179" t="s">
+      <c r="R179" t="s">
+        <v>202</v>
+      </c>
+      <c r="S179" t="s">
         <v>192</v>
-      </c>
-      <c r="R179" t="s">
-        <v>193</v>
-      </c>
-      <c r="S179" t="s">
-        <v>194</v>
       </c>
       <c r="V179">
         <v>1</v>
@@ -15117,34 +15128,34 @@
         <v>1.200234016</v>
       </c>
       <c r="G180" t="s">
+        <v>188</v>
+      </c>
+      <c r="I180" t="s">
         <v>189</v>
       </c>
-      <c r="I180" t="s">
+      <c r="K180" t="s">
+        <v>189</v>
+      </c>
+      <c r="L180">
+        <v>1</v>
+      </c>
+      <c r="N180" t="s">
+        <v>65</v>
+      </c>
+      <c r="O180" t="s">
         <v>190</v>
       </c>
-      <c r="K180" t="s">
-        <v>190</v>
-      </c>
-      <c r="L180">
-        <v>1</v>
-      </c>
-      <c r="N180" t="s">
-        <v>65</v>
-      </c>
-      <c r="O180" t="s">
+      <c r="P180" s="5">
+        <v>5057805794592</v>
+      </c>
+      <c r="Q180" t="s">
         <v>191</v>
       </c>
-      <c r="P180">
-        <v>5057805794660</v>
-      </c>
-      <c r="Q180" t="s">
+      <c r="R180" t="s">
+        <v>202</v>
+      </c>
+      <c r="S180" t="s">
         <v>192</v>
-      </c>
-      <c r="R180" t="s">
-        <v>193</v>
-      </c>
-      <c r="S180" t="s">
-        <v>194</v>
       </c>
       <c r="V180">
         <v>2</v>
@@ -15200,34 +15211,34 @@
         <v>1.200234016</v>
       </c>
       <c r="G181" t="s">
+        <v>188</v>
+      </c>
+      <c r="I181" t="s">
         <v>189</v>
       </c>
-      <c r="I181" t="s">
+      <c r="K181" t="s">
+        <v>189</v>
+      </c>
+      <c r="L181">
+        <v>1</v>
+      </c>
+      <c r="N181" t="s">
+        <v>65</v>
+      </c>
+      <c r="O181" t="s">
         <v>190</v>
       </c>
-      <c r="K181" t="s">
-        <v>190</v>
-      </c>
-      <c r="L181">
-        <v>1</v>
-      </c>
-      <c r="N181" t="s">
-        <v>65</v>
-      </c>
-      <c r="O181" t="s">
+      <c r="P181">
+        <v>5057805794592</v>
+      </c>
+      <c r="Q181" t="s">
         <v>191</v>
       </c>
-      <c r="P181">
-        <v>5057805794660</v>
-      </c>
-      <c r="Q181" t="s">
+      <c r="R181" t="s">
+        <v>202</v>
+      </c>
+      <c r="S181" t="s">
         <v>192</v>
-      </c>
-      <c r="R181" t="s">
-        <v>193</v>
-      </c>
-      <c r="S181" t="s">
-        <v>194</v>
       </c>
       <c r="V181">
         <v>4</v>
@@ -15283,34 +15294,34 @@
         <v>1.200234016</v>
       </c>
       <c r="G182" t="s">
+        <v>188</v>
+      </c>
+      <c r="I182" t="s">
         <v>189</v>
       </c>
-      <c r="I182" t="s">
+      <c r="K182" t="s">
+        <v>189</v>
+      </c>
+      <c r="L182">
+        <v>1</v>
+      </c>
+      <c r="N182" t="s">
+        <v>65</v>
+      </c>
+      <c r="O182" t="s">
         <v>190</v>
       </c>
-      <c r="K182" t="s">
-        <v>190</v>
-      </c>
-      <c r="L182">
-        <v>1</v>
-      </c>
-      <c r="N182" t="s">
-        <v>65</v>
-      </c>
-      <c r="O182" t="s">
+      <c r="P182" s="5">
+        <v>5057805794592</v>
+      </c>
+      <c r="Q182" t="s">
         <v>191</v>
       </c>
-      <c r="P182">
-        <v>5057805794660</v>
-      </c>
-      <c r="Q182" t="s">
+      <c r="R182" t="s">
+        <v>202</v>
+      </c>
+      <c r="S182" t="s">
         <v>192</v>
-      </c>
-      <c r="R182" t="s">
-        <v>193</v>
-      </c>
-      <c r="S182" t="s">
-        <v>194</v>
       </c>
       <c r="V182">
         <v>2</v>
@@ -15351,7 +15362,7 @@
         <v>60</v>
       </c>
       <c r="B183" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C183" s="2">
         <v>44743</v>
@@ -15366,34 +15377,34 @@
         <v>1.20023415</v>
       </c>
       <c r="G183" t="s">
+        <v>188</v>
+      </c>
+      <c r="I183" t="s">
         <v>189</v>
       </c>
-      <c r="I183" t="s">
+      <c r="K183" t="s">
+        <v>189</v>
+      </c>
+      <c r="L183">
+        <v>1</v>
+      </c>
+      <c r="N183" t="s">
+        <v>65</v>
+      </c>
+      <c r="O183" t="s">
         <v>190</v>
       </c>
-      <c r="K183" t="s">
-        <v>190</v>
-      </c>
-      <c r="L183">
-        <v>1</v>
-      </c>
-      <c r="N183" t="s">
-        <v>65</v>
-      </c>
-      <c r="O183" t="s">
+      <c r="P183">
+        <v>5057805794592</v>
+      </c>
+      <c r="Q183" t="s">
         <v>191</v>
       </c>
-      <c r="P183">
-        <v>5057805794660</v>
-      </c>
-      <c r="Q183" t="s">
+      <c r="R183" t="s">
+        <v>202</v>
+      </c>
+      <c r="S183" t="s">
         <v>192</v>
-      </c>
-      <c r="R183" t="s">
-        <v>193</v>
-      </c>
-      <c r="S183" t="s">
-        <v>194</v>
       </c>
       <c r="V183">
         <v>2</v>
@@ -15449,16 +15460,16 @@
         <v>1.1422334949999999</v>
       </c>
       <c r="G184" t="s">
+        <v>188</v>
+      </c>
+      <c r="I184" t="s">
         <v>189</v>
       </c>
-      <c r="I184" t="s">
-        <v>190</v>
-      </c>
       <c r="J184" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="K184" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L184">
         <v>1</v>
@@ -15469,14 +15480,14 @@
       <c r="N184" t="s">
         <v>65</v>
       </c>
-      <c r="P184">
-        <v>5057805794660</v>
+      <c r="P184" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q184" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="R184" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="V184">
         <v>0</v>
@@ -15532,35 +15543,35 @@
         <v>1.200234016</v>
       </c>
       <c r="G185" t="s">
+        <v>188</v>
+      </c>
+      <c r="I185" t="s">
         <v>189</v>
       </c>
-      <c r="I185" t="s">
+      <c r="K185" t="s">
+        <v>189</v>
+      </c>
+      <c r="L185">
+        <v>1</v>
+      </c>
+      <c r="N185" t="s">
+        <v>65</v>
+      </c>
+      <c r="O185" t="s">
         <v>190</v>
       </c>
-      <c r="K185" t="s">
-        <v>190</v>
-      </c>
-      <c r="L185">
-        <v>1</v>
-      </c>
-      <c r="N185" t="s">
-        <v>65</v>
-      </c>
-      <c r="O185" t="s">
+      <c r="P185">
+        <v>5057805794592</v>
+      </c>
+      <c r="Q185" t="s">
         <v>191</v>
       </c>
-      <c r="P185">
-        <v>5057805794660</v>
-      </c>
-      <c r="Q185" t="s">
+      <c r="R185" t="s">
+        <v>202</v>
+      </c>
+      <c r="S185" t="s">
         <v>192</v>
       </c>
-      <c r="R185" t="s">
-        <v>193</v>
-      </c>
-      <c r="S185" t="s">
-        <v>194</v>
-      </c>
       <c r="V185">
         <v>1</v>
       </c>
@@ -15568,7 +15579,7 @@
         <v>69</v>
       </c>
       <c r="Y185" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="AB185">
         <v>1</v>
@@ -15615,34 +15626,34 @@
         <v>1.200234016</v>
       </c>
       <c r="G186" t="s">
+        <v>188</v>
+      </c>
+      <c r="I186" t="s">
         <v>189</v>
       </c>
-      <c r="I186" t="s">
+      <c r="K186" t="s">
+        <v>189</v>
+      </c>
+      <c r="L186">
+        <v>1</v>
+      </c>
+      <c r="N186" t="s">
+        <v>65</v>
+      </c>
+      <c r="O186" t="s">
         <v>190</v>
       </c>
-      <c r="K186" t="s">
-        <v>190</v>
-      </c>
-      <c r="L186">
-        <v>1</v>
-      </c>
-      <c r="N186" t="s">
-        <v>65</v>
-      </c>
-      <c r="O186" t="s">
+      <c r="P186" s="5">
+        <v>5057805794592</v>
+      </c>
+      <c r="Q186" t="s">
         <v>191</v>
       </c>
-      <c r="P186">
-        <v>5057805794660</v>
-      </c>
-      <c r="Q186" t="s">
+      <c r="R186" t="s">
+        <v>202</v>
+      </c>
+      <c r="S186" t="s">
         <v>192</v>
-      </c>
-      <c r="R186" t="s">
-        <v>193</v>
-      </c>
-      <c r="S186" t="s">
-        <v>194</v>
       </c>
       <c r="V186">
         <v>5</v>
@@ -15698,34 +15709,34 @@
         <v>1.200234016</v>
       </c>
       <c r="G187" t="s">
+        <v>188</v>
+      </c>
+      <c r="I187" t="s">
         <v>189</v>
       </c>
-      <c r="I187" t="s">
+      <c r="K187" t="s">
+        <v>189</v>
+      </c>
+      <c r="L187">
+        <v>1</v>
+      </c>
+      <c r="N187" t="s">
+        <v>65</v>
+      </c>
+      <c r="O187" t="s">
         <v>190</v>
       </c>
-      <c r="K187" t="s">
-        <v>190</v>
-      </c>
-      <c r="L187">
-        <v>1</v>
-      </c>
-      <c r="N187" t="s">
-        <v>65</v>
-      </c>
-      <c r="O187" t="s">
+      <c r="P187">
+        <v>5057805794592</v>
+      </c>
+      <c r="Q187" t="s">
         <v>191</v>
       </c>
-      <c r="P187">
-        <v>5057805794660</v>
-      </c>
-      <c r="Q187" t="s">
+      <c r="R187" t="s">
+        <v>202</v>
+      </c>
+      <c r="S187" t="s">
         <v>192</v>
-      </c>
-      <c r="R187" t="s">
-        <v>193</v>
-      </c>
-      <c r="S187" t="s">
-        <v>194</v>
       </c>
       <c r="V187">
         <v>1</v>
@@ -15781,34 +15792,34 @@
         <v>1.200234016</v>
       </c>
       <c r="G188" t="s">
+        <v>188</v>
+      </c>
+      <c r="I188" t="s">
         <v>189</v>
       </c>
-      <c r="I188" t="s">
+      <c r="K188" t="s">
+        <v>189</v>
+      </c>
+      <c r="L188">
+        <v>1</v>
+      </c>
+      <c r="N188" t="s">
+        <v>65</v>
+      </c>
+      <c r="O188" t="s">
         <v>190</v>
       </c>
-      <c r="K188" t="s">
-        <v>190</v>
-      </c>
-      <c r="L188">
-        <v>1</v>
-      </c>
-      <c r="N188" t="s">
-        <v>65</v>
-      </c>
-      <c r="O188" t="s">
+      <c r="P188" s="5">
+        <v>5057805794592</v>
+      </c>
+      <c r="Q188" t="s">
         <v>191</v>
       </c>
-      <c r="P188">
-        <v>5057805794660</v>
-      </c>
-      <c r="Q188" t="s">
+      <c r="R188" t="s">
+        <v>202</v>
+      </c>
+      <c r="S188" t="s">
         <v>192</v>
-      </c>
-      <c r="R188" t="s">
-        <v>193</v>
-      </c>
-      <c r="S188" t="s">
-        <v>194</v>
       </c>
       <c r="V188">
         <v>6</v>
@@ -15849,7 +15860,7 @@
         <v>60</v>
       </c>
       <c r="B189" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C189" s="2">
         <v>44743</v>
@@ -15864,34 +15875,34 @@
         <v>1.2002341050000001</v>
       </c>
       <c r="G189" t="s">
+        <v>188</v>
+      </c>
+      <c r="I189" t="s">
         <v>189</v>
       </c>
-      <c r="I189" t="s">
+      <c r="K189" t="s">
+        <v>189</v>
+      </c>
+      <c r="L189">
+        <v>1</v>
+      </c>
+      <c r="N189" t="s">
+        <v>65</v>
+      </c>
+      <c r="O189" t="s">
         <v>190</v>
       </c>
-      <c r="K189" t="s">
-        <v>190</v>
-      </c>
-      <c r="L189">
-        <v>1</v>
-      </c>
-      <c r="N189" t="s">
-        <v>65</v>
-      </c>
-      <c r="O189" t="s">
+      <c r="P189">
+        <v>5057805794592</v>
+      </c>
+      <c r="Q189" t="s">
         <v>191</v>
       </c>
-      <c r="P189">
-        <v>5057805794660</v>
-      </c>
-      <c r="Q189" t="s">
+      <c r="R189" t="s">
+        <v>202</v>
+      </c>
+      <c r="S189" t="s">
         <v>192</v>
-      </c>
-      <c r="R189" t="s">
-        <v>193</v>
-      </c>
-      <c r="S189" t="s">
-        <v>194</v>
       </c>
       <c r="V189">
         <v>1</v>
@@ -15947,34 +15958,34 @@
         <v>1.200234016</v>
       </c>
       <c r="G190" t="s">
+        <v>188</v>
+      </c>
+      <c r="I190" t="s">
         <v>189</v>
       </c>
-      <c r="I190" t="s">
+      <c r="K190" t="s">
+        <v>189</v>
+      </c>
+      <c r="L190">
+        <v>1</v>
+      </c>
+      <c r="N190" t="s">
+        <v>65</v>
+      </c>
+      <c r="O190" t="s">
         <v>190</v>
       </c>
-      <c r="K190" t="s">
-        <v>190</v>
-      </c>
-      <c r="L190">
-        <v>1</v>
-      </c>
-      <c r="N190" t="s">
-        <v>65</v>
-      </c>
-      <c r="O190" t="s">
+      <c r="P190" s="5">
+        <v>5057805794592</v>
+      </c>
+      <c r="Q190" t="s">
         <v>191</v>
       </c>
-      <c r="P190">
-        <v>5057805794660</v>
-      </c>
-      <c r="Q190" t="s">
+      <c r="R190" t="s">
+        <v>202</v>
+      </c>
+      <c r="S190" t="s">
         <v>192</v>
-      </c>
-      <c r="R190" t="s">
-        <v>193</v>
-      </c>
-      <c r="S190" t="s">
-        <v>194</v>
       </c>
       <c r="V190">
         <v>5</v>
@@ -16030,34 +16041,34 @@
         <v>1.200234016</v>
       </c>
       <c r="G191" t="s">
+        <v>188</v>
+      </c>
+      <c r="I191" t="s">
         <v>189</v>
       </c>
-      <c r="I191" t="s">
+      <c r="K191" t="s">
+        <v>189</v>
+      </c>
+      <c r="L191">
+        <v>1</v>
+      </c>
+      <c r="N191" t="s">
+        <v>65</v>
+      </c>
+      <c r="O191" t="s">
         <v>190</v>
       </c>
-      <c r="K191" t="s">
-        <v>190</v>
-      </c>
-      <c r="L191">
-        <v>1</v>
-      </c>
-      <c r="N191" t="s">
-        <v>65</v>
-      </c>
-      <c r="O191" t="s">
+      <c r="P191">
+        <v>5057805794592</v>
+      </c>
+      <c r="Q191" t="s">
         <v>191</v>
       </c>
-      <c r="P191">
-        <v>5057805794660</v>
-      </c>
-      <c r="Q191" t="s">
+      <c r="R191" t="s">
+        <v>202</v>
+      </c>
+      <c r="S191" t="s">
         <v>192</v>
-      </c>
-      <c r="R191" t="s">
-        <v>193</v>
-      </c>
-      <c r="S191" t="s">
-        <v>194</v>
       </c>
       <c r="V191">
         <v>3</v>
@@ -16098,7 +16109,7 @@
         <v>60</v>
       </c>
       <c r="B192" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C192" s="2">
         <v>44743</v>
@@ -16113,34 +16124,34 @@
         <v>1.2002341050000001</v>
       </c>
       <c r="G192" t="s">
+        <v>188</v>
+      </c>
+      <c r="I192" t="s">
         <v>189</v>
       </c>
-      <c r="I192" t="s">
+      <c r="K192" t="s">
+        <v>189</v>
+      </c>
+      <c r="L192">
+        <v>1</v>
+      </c>
+      <c r="N192" t="s">
+        <v>65</v>
+      </c>
+      <c r="O192" t="s">
         <v>190</v>
       </c>
-      <c r="K192" t="s">
-        <v>190</v>
-      </c>
-      <c r="L192">
-        <v>1</v>
-      </c>
-      <c r="N192" t="s">
-        <v>65</v>
-      </c>
-      <c r="O192" t="s">
+      <c r="P192" s="5">
+        <v>5057805794592</v>
+      </c>
+      <c r="Q192" t="s">
         <v>191</v>
       </c>
-      <c r="P192">
-        <v>5057805794660</v>
-      </c>
-      <c r="Q192" t="s">
+      <c r="R192" t="s">
+        <v>202</v>
+      </c>
+      <c r="S192" t="s">
         <v>192</v>
-      </c>
-      <c r="R192" t="s">
-        <v>193</v>
-      </c>
-      <c r="S192" t="s">
-        <v>194</v>
       </c>
       <c r="V192">
         <v>1</v>
@@ -16181,7 +16192,7 @@
         <v>60</v>
       </c>
       <c r="B193" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C193" s="2">
         <v>44743</v>
@@ -16196,34 +16207,34 @@
         <v>1.2002341050000001</v>
       </c>
       <c r="G193" t="s">
+        <v>188</v>
+      </c>
+      <c r="I193" t="s">
         <v>189</v>
       </c>
-      <c r="I193" t="s">
+      <c r="K193" t="s">
+        <v>189</v>
+      </c>
+      <c r="L193">
+        <v>1</v>
+      </c>
+      <c r="N193" t="s">
+        <v>65</v>
+      </c>
+      <c r="O193" t="s">
         <v>190</v>
       </c>
-      <c r="K193" t="s">
-        <v>190</v>
-      </c>
-      <c r="L193">
-        <v>1</v>
-      </c>
-      <c r="N193" t="s">
-        <v>65</v>
-      </c>
-      <c r="O193" t="s">
+      <c r="P193">
+        <v>5057805794592</v>
+      </c>
+      <c r="Q193" t="s">
         <v>191</v>
       </c>
-      <c r="P193">
-        <v>5057805794660</v>
-      </c>
-      <c r="Q193" t="s">
+      <c r="R193" t="s">
+        <v>202</v>
+      </c>
+      <c r="S193" t="s">
         <v>192</v>
-      </c>
-      <c r="R193" t="s">
-        <v>193</v>
-      </c>
-      <c r="S193" t="s">
-        <v>194</v>
       </c>
       <c r="V193">
         <v>1</v>
@@ -16279,34 +16290,34 @@
         <v>1.200234016</v>
       </c>
       <c r="G194" t="s">
+        <v>188</v>
+      </c>
+      <c r="I194" t="s">
         <v>189</v>
       </c>
-      <c r="I194" t="s">
+      <c r="K194" t="s">
+        <v>189</v>
+      </c>
+      <c r="L194">
+        <v>1</v>
+      </c>
+      <c r="N194" t="s">
+        <v>65</v>
+      </c>
+      <c r="O194" t="s">
         <v>190</v>
       </c>
-      <c r="K194" t="s">
-        <v>190</v>
-      </c>
-      <c r="L194">
-        <v>1</v>
-      </c>
-      <c r="N194" t="s">
-        <v>65</v>
-      </c>
-      <c r="O194" t="s">
+      <c r="P194" s="5">
+        <v>5057805794592</v>
+      </c>
+      <c r="Q194" t="s">
         <v>191</v>
       </c>
-      <c r="P194">
-        <v>5057805794660</v>
-      </c>
-      <c r="Q194" t="s">
+      <c r="R194" t="s">
+        <v>202</v>
+      </c>
+      <c r="S194" t="s">
         <v>192</v>
-      </c>
-      <c r="R194" t="s">
-        <v>193</v>
-      </c>
-      <c r="S194" t="s">
-        <v>194</v>
       </c>
       <c r="V194">
         <v>7</v>
@@ -16362,34 +16373,34 @@
         <v>1.200234016</v>
       </c>
       <c r="G195" t="s">
+        <v>188</v>
+      </c>
+      <c r="I195" t="s">
         <v>189</v>
       </c>
-      <c r="I195" t="s">
+      <c r="K195" t="s">
+        <v>189</v>
+      </c>
+      <c r="L195">
+        <v>1</v>
+      </c>
+      <c r="N195" t="s">
+        <v>65</v>
+      </c>
+      <c r="O195" t="s">
         <v>190</v>
       </c>
-      <c r="K195" t="s">
-        <v>190</v>
-      </c>
-      <c r="L195">
-        <v>1</v>
-      </c>
-      <c r="N195" t="s">
-        <v>65</v>
-      </c>
-      <c r="O195" t="s">
+      <c r="P195">
+        <v>5057805794592</v>
+      </c>
+      <c r="Q195" t="s">
         <v>191</v>
       </c>
-      <c r="P195">
-        <v>5057805794660</v>
-      </c>
-      <c r="Q195" t="s">
+      <c r="R195" t="s">
+        <v>202</v>
+      </c>
+      <c r="S195" t="s">
         <v>192</v>
-      </c>
-      <c r="R195" t="s">
-        <v>193</v>
-      </c>
-      <c r="S195" t="s">
-        <v>194</v>
       </c>
       <c r="V195">
         <v>2</v>
@@ -16445,16 +16456,16 @@
         <v>1.1422334949999999</v>
       </c>
       <c r="G196" t="s">
+        <v>188</v>
+      </c>
+      <c r="I196" t="s">
         <v>189</v>
       </c>
-      <c r="I196" t="s">
-        <v>190</v>
-      </c>
       <c r="J196" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="K196" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L196">
         <v>1</v>
@@ -16465,14 +16476,14 @@
       <c r="N196" t="s">
         <v>65</v>
       </c>
-      <c r="P196">
-        <v>5057805794660</v>
+      <c r="P196" s="5">
+        <v>5057805794592</v>
       </c>
       <c r="Q196" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="R196" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="V196">
         <v>0</v>
@@ -16528,34 +16539,34 @@
         <v>1.200234016</v>
       </c>
       <c r="G197" t="s">
+        <v>188</v>
+      </c>
+      <c r="I197" t="s">
         <v>189</v>
       </c>
-      <c r="I197" t="s">
+      <c r="K197" t="s">
+        <v>189</v>
+      </c>
+      <c r="L197">
+        <v>1</v>
+      </c>
+      <c r="N197" t="s">
+        <v>65</v>
+      </c>
+      <c r="O197" t="s">
         <v>190</v>
       </c>
-      <c r="K197" t="s">
-        <v>190</v>
-      </c>
-      <c r="L197">
-        <v>1</v>
-      </c>
-      <c r="N197" t="s">
-        <v>65</v>
-      </c>
-      <c r="O197" t="s">
+      <c r="P197">
+        <v>5057805794592</v>
+      </c>
+      <c r="Q197" t="s">
         <v>191</v>
       </c>
-      <c r="P197">
-        <v>5057805794660</v>
-      </c>
-      <c r="Q197" t="s">
+      <c r="R197" t="s">
+        <v>202</v>
+      </c>
+      <c r="S197" t="s">
         <v>192</v>
-      </c>
-      <c r="R197" t="s">
-        <v>193</v>
-      </c>
-      <c r="S197" t="s">
-        <v>194</v>
       </c>
       <c r="V197">
         <v>2</v>
@@ -16611,34 +16622,34 @@
         <v>1.200234016</v>
       </c>
       <c r="G198" t="s">
+        <v>188</v>
+      </c>
+      <c r="I198" t="s">
         <v>189</v>
       </c>
-      <c r="I198" t="s">
+      <c r="K198" t="s">
+        <v>189</v>
+      </c>
+      <c r="L198">
+        <v>1</v>
+      </c>
+      <c r="N198" t="s">
+        <v>65</v>
+      </c>
+      <c r="O198" t="s">
         <v>190</v>
       </c>
-      <c r="K198" t="s">
-        <v>190</v>
-      </c>
-      <c r="L198">
-        <v>1</v>
-      </c>
-      <c r="N198" t="s">
-        <v>65</v>
-      </c>
-      <c r="O198" t="s">
+      <c r="P198" s="5">
+        <v>5057805794592</v>
+      </c>
+      <c r="Q198" t="s">
         <v>191</v>
       </c>
-      <c r="P198">
-        <v>5057805794660</v>
-      </c>
-      <c r="Q198" t="s">
+      <c r="R198" t="s">
+        <v>202</v>
+      </c>
+      <c r="S198" t="s">
         <v>192</v>
-      </c>
-      <c r="R198" t="s">
-        <v>193</v>
-      </c>
-      <c r="S198" t="s">
-        <v>194</v>
       </c>
       <c r="V198">
         <v>1</v>
@@ -16694,34 +16705,34 @@
         <v>1.200234016</v>
       </c>
       <c r="G199" t="s">
+        <v>188</v>
+      </c>
+      <c r="I199" t="s">
         <v>189</v>
       </c>
-      <c r="I199" t="s">
+      <c r="K199" t="s">
+        <v>189</v>
+      </c>
+      <c r="L199">
+        <v>1</v>
+      </c>
+      <c r="N199" t="s">
+        <v>65</v>
+      </c>
+      <c r="O199" t="s">
         <v>190</v>
       </c>
-      <c r="K199" t="s">
-        <v>190</v>
-      </c>
-      <c r="L199">
-        <v>1</v>
-      </c>
-      <c r="N199" t="s">
-        <v>65</v>
-      </c>
-      <c r="O199" t="s">
+      <c r="P199">
+        <v>5057805794592</v>
+      </c>
+      <c r="Q199" t="s">
         <v>191</v>
       </c>
-      <c r="P199">
-        <v>5057805794660</v>
-      </c>
-      <c r="Q199" t="s">
+      <c r="R199" t="s">
+        <v>202</v>
+      </c>
+      <c r="S199" t="s">
         <v>192</v>
-      </c>
-      <c r="R199" t="s">
-        <v>193</v>
-      </c>
-      <c r="S199" t="s">
-        <v>194</v>
       </c>
       <c r="V199">
         <v>6</v>
@@ -16777,34 +16788,34 @@
         <v>1.200234016</v>
       </c>
       <c r="G200" t="s">
+        <v>188</v>
+      </c>
+      <c r="I200" t="s">
         <v>189</v>
       </c>
-      <c r="I200" t="s">
+      <c r="K200" t="s">
+        <v>189</v>
+      </c>
+      <c r="L200">
+        <v>1</v>
+      </c>
+      <c r="N200" t="s">
+        <v>65</v>
+      </c>
+      <c r="O200" t="s">
         <v>190</v>
       </c>
-      <c r="K200" t="s">
-        <v>190</v>
-      </c>
-      <c r="L200">
-        <v>1</v>
-      </c>
-      <c r="N200" t="s">
-        <v>65</v>
-      </c>
-      <c r="O200" t="s">
+      <c r="P200" s="5">
+        <v>5057805794592</v>
+      </c>
+      <c r="Q200" t="s">
         <v>191</v>
       </c>
-      <c r="P200">
-        <v>5057805794660</v>
-      </c>
-      <c r="Q200" t="s">
+      <c r="R200" t="s">
+        <v>202</v>
+      </c>
+      <c r="S200" t="s">
         <v>192</v>
-      </c>
-      <c r="R200" t="s">
-        <v>193</v>
-      </c>
-      <c r="S200" t="s">
-        <v>194</v>
       </c>
       <c r="V200">
         <v>2</v>
@@ -16860,16 +16871,16 @@
         <v>1.1422334949999999</v>
       </c>
       <c r="G201" t="s">
+        <v>188</v>
+      </c>
+      <c r="I201" t="s">
         <v>189</v>
       </c>
-      <c r="I201" t="s">
-        <v>190</v>
-      </c>
       <c r="J201" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="K201" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L201">
         <v>1</v>
@@ -16881,13 +16892,13 @@
         <v>65</v>
       </c>
       <c r="P201">
-        <v>5057805794660</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q201" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="R201" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="V201">
         <v>0</v>
@@ -16943,34 +16954,34 @@
         <v>1.200234016</v>
       </c>
       <c r="G202" t="s">
+        <v>188</v>
+      </c>
+      <c r="I202" t="s">
         <v>189</v>
       </c>
-      <c r="I202" t="s">
+      <c r="K202" t="s">
+        <v>189</v>
+      </c>
+      <c r="L202">
+        <v>1</v>
+      </c>
+      <c r="N202" t="s">
+        <v>65</v>
+      </c>
+      <c r="O202" t="s">
         <v>190</v>
       </c>
-      <c r="K202" t="s">
-        <v>190</v>
-      </c>
-      <c r="L202">
-        <v>1</v>
-      </c>
-      <c r="N202" t="s">
-        <v>65</v>
-      </c>
-      <c r="O202" t="s">
+      <c r="P202" s="5">
+        <v>5057805794592</v>
+      </c>
+      <c r="Q202" t="s">
         <v>191</v>
       </c>
-      <c r="P202">
-        <v>5057805794660</v>
-      </c>
-      <c r="Q202" t="s">
+      <c r="R202" t="s">
+        <v>202</v>
+      </c>
+      <c r="S202" t="s">
         <v>192</v>
-      </c>
-      <c r="R202" t="s">
-        <v>193</v>
-      </c>
-      <c r="S202" t="s">
-        <v>194</v>
       </c>
       <c r="V202">
         <v>3</v>
@@ -17026,16 +17037,16 @@
         <v>1.1422334949999999</v>
       </c>
       <c r="G203" t="s">
+        <v>188</v>
+      </c>
+      <c r="I203" t="s">
         <v>189</v>
       </c>
-      <c r="I203" t="s">
-        <v>190</v>
-      </c>
       <c r="J203" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="K203" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L203">
         <v>1</v>
@@ -17047,13 +17058,13 @@
         <v>65</v>
       </c>
       <c r="P203">
-        <v>5057805794660</v>
+        <v>5057805794592</v>
       </c>
       <c r="Q203" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="R203" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="V203">
         <v>0</v>
@@ -17109,34 +17120,34 @@
         <v>1.200234016</v>
       </c>
       <c r="G204" t="s">
+        <v>188</v>
+      </c>
+      <c r="I204" t="s">
         <v>189</v>
       </c>
-      <c r="I204" t="s">
+      <c r="K204" t="s">
+        <v>189</v>
+      </c>
+      <c r="L204">
+        <v>1</v>
+      </c>
+      <c r="N204" t="s">
+        <v>65</v>
+      </c>
+      <c r="O204" t="s">
         <v>190</v>
       </c>
-      <c r="K204" t="s">
-        <v>190</v>
-      </c>
-      <c r="L204">
-        <v>1</v>
-      </c>
-      <c r="N204" t="s">
-        <v>65</v>
-      </c>
-      <c r="O204" t="s">
+      <c r="P204" s="5">
+        <v>5057805794592</v>
+      </c>
+      <c r="Q204" t="s">
         <v>191</v>
       </c>
-      <c r="P204">
-        <v>5057805794660</v>
-      </c>
-      <c r="Q204" t="s">
+      <c r="R204" t="s">
+        <v>202</v>
+      </c>
+      <c r="S204" t="s">
         <v>192</v>
-      </c>
-      <c r="R204" t="s">
-        <v>193</v>
-      </c>
-      <c r="S204" t="s">
-        <v>194</v>
       </c>
       <c r="V204">
         <v>4</v>
@@ -17192,34 +17203,34 @@
         <v>1.200234016</v>
       </c>
       <c r="G205" t="s">
+        <v>188</v>
+      </c>
+      <c r="I205" t="s">
         <v>189</v>
       </c>
-      <c r="I205" t="s">
+      <c r="K205" t="s">
+        <v>189</v>
+      </c>
+      <c r="L205">
+        <v>1</v>
+      </c>
+      <c r="N205" t="s">
+        <v>65</v>
+      </c>
+      <c r="O205" t="s">
         <v>190</v>
       </c>
-      <c r="K205" t="s">
-        <v>190</v>
-      </c>
-      <c r="L205">
-        <v>1</v>
-      </c>
-      <c r="N205" t="s">
-        <v>65</v>
-      </c>
-      <c r="O205" t="s">
+      <c r="P205">
+        <v>5057805794592</v>
+      </c>
+      <c r="Q205" t="s">
         <v>191</v>
       </c>
-      <c r="P205">
-        <v>5057805794660</v>
-      </c>
-      <c r="Q205" t="s">
+      <c r="R205" t="s">
+        <v>202</v>
+      </c>
+      <c r="S205" t="s">
         <v>192</v>
-      </c>
-      <c r="R205" t="s">
-        <v>193</v>
-      </c>
-      <c r="S205" t="s">
-        <v>194</v>
       </c>
       <c r="V205">
         <v>3</v>
@@ -17275,34 +17286,34 @@
         <v>1.200234016</v>
       </c>
       <c r="G206" t="s">
+        <v>188</v>
+      </c>
+      <c r="I206" t="s">
         <v>189</v>
       </c>
-      <c r="I206" t="s">
+      <c r="K206" t="s">
+        <v>189</v>
+      </c>
+      <c r="L206">
+        <v>1</v>
+      </c>
+      <c r="N206" t="s">
+        <v>65</v>
+      </c>
+      <c r="O206" t="s">
         <v>190</v>
       </c>
-      <c r="K206" t="s">
-        <v>190</v>
-      </c>
-      <c r="L206">
-        <v>1</v>
-      </c>
-      <c r="N206" t="s">
-        <v>65</v>
-      </c>
-      <c r="O206" t="s">
+      <c r="P206" s="5">
+        <v>5057805794592</v>
+      </c>
+      <c r="Q206" t="s">
         <v>191</v>
       </c>
-      <c r="P206">
-        <v>5057805794660</v>
-      </c>
-      <c r="Q206" t="s">
+      <c r="R206" t="s">
+        <v>202</v>
+      </c>
+      <c r="S206" t="s">
         <v>192</v>
-      </c>
-      <c r="R206" t="s">
-        <v>193</v>
-      </c>
-      <c r="S206" t="s">
-        <v>194</v>
       </c>
       <c r="V206">
         <v>2</v>
@@ -17358,34 +17369,34 @@
         <v>1.200234016</v>
       </c>
       <c r="G207" t="s">
+        <v>188</v>
+      </c>
+      <c r="I207" t="s">
         <v>189</v>
       </c>
-      <c r="I207" t="s">
+      <c r="K207" t="s">
+        <v>189</v>
+      </c>
+      <c r="L207">
+        <v>1</v>
+      </c>
+      <c r="N207" t="s">
+        <v>65</v>
+      </c>
+      <c r="O207" t="s">
         <v>190</v>
       </c>
-      <c r="K207" t="s">
-        <v>190</v>
-      </c>
-      <c r="L207">
-        <v>1</v>
-      </c>
-      <c r="N207" t="s">
-        <v>65</v>
-      </c>
-      <c r="O207" t="s">
+      <c r="P207">
+        <v>5057805794592</v>
+      </c>
+      <c r="Q207" t="s">
         <v>191</v>
       </c>
-      <c r="P207">
-        <v>5057805794660</v>
-      </c>
-      <c r="Q207" t="s">
+      <c r="R207" t="s">
+        <v>202</v>
+      </c>
+      <c r="S207" t="s">
         <v>192</v>
-      </c>
-      <c r="R207" t="s">
-        <v>193</v>
-      </c>
-      <c r="S207" t="s">
-        <v>194</v>
       </c>
       <c r="V207">
         <v>7</v>
@@ -17441,34 +17452,34 @@
         <v>1.200234016</v>
       </c>
       <c r="G208" t="s">
+        <v>188</v>
+      </c>
+      <c r="I208" t="s">
         <v>189</v>
       </c>
-      <c r="I208" t="s">
+      <c r="K208" t="s">
+        <v>189</v>
+      </c>
+      <c r="L208">
+        <v>1</v>
+      </c>
+      <c r="N208" t="s">
+        <v>65</v>
+      </c>
+      <c r="O208" t="s">
         <v>190</v>
       </c>
-      <c r="K208" t="s">
-        <v>190</v>
-      </c>
-      <c r="L208">
-        <v>1</v>
-      </c>
-      <c r="N208" t="s">
-        <v>65</v>
-      </c>
-      <c r="O208" t="s">
+      <c r="P208" s="5">
+        <v>5057805794592</v>
+      </c>
+      <c r="Q208" t="s">
         <v>191</v>
       </c>
-      <c r="P208">
-        <v>5057805794660</v>
-      </c>
-      <c r="Q208" t="s">
+      <c r="R208" t="s">
+        <v>202</v>
+      </c>
+      <c r="S208" t="s">
         <v>192</v>
-      </c>
-      <c r="R208" t="s">
-        <v>193</v>
-      </c>
-      <c r="S208" t="s">
-        <v>194</v>
       </c>
       <c r="V208">
         <v>1</v>
@@ -17524,34 +17535,34 @@
         <v>1.200234016</v>
       </c>
       <c r="G209" t="s">
+        <v>188</v>
+      </c>
+      <c r="I209" t="s">
         <v>189</v>
       </c>
-      <c r="I209" t="s">
+      <c r="K209" t="s">
+        <v>189</v>
+      </c>
+      <c r="L209">
+        <v>1</v>
+      </c>
+      <c r="N209" t="s">
+        <v>65</v>
+      </c>
+      <c r="O209" t="s">
         <v>190</v>
       </c>
-      <c r="K209" t="s">
-        <v>190</v>
-      </c>
-      <c r="L209">
-        <v>1</v>
-      </c>
-      <c r="N209" t="s">
-        <v>65</v>
-      </c>
-      <c r="O209" t="s">
+      <c r="P209">
+        <v>5057805794592</v>
+      </c>
+      <c r="Q209" t="s">
         <v>191</v>
       </c>
-      <c r="P209">
-        <v>5057805794660</v>
-      </c>
-      <c r="Q209" t="s">
+      <c r="R209" t="s">
+        <v>202</v>
+      </c>
+      <c r="S209" t="s">
         <v>192</v>
-      </c>
-      <c r="R209" t="s">
-        <v>193</v>
-      </c>
-      <c r="S209" t="s">
-        <v>194</v>
       </c>
       <c r="V209">
         <v>4</v>
@@ -17588,7 +17599,9 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -17599,12 +17612,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>
